--- a/WorkBot/refactor-experimental/data/orders/UNFI/UNFI_Bakery_20260307.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/UNFI/UNFI_Bakery_20260307.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1178,6 +1178,27 @@
         <v>50.12</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>151396-9</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Simply - Raspberry Lemonade</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="E37" t="n">
+        <v>18.43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
